--- a/artfynd/A 45602-2025 artfynd.xlsx
+++ b/artfynd/A 45602-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6750091</v>
+        <v>66998874</v>
       </c>
       <c r="B2" t="n">
-        <v>95220</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2609</v>
+        <v>73</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsfliksmossa</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lejeunea cavifolia</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ehrh.) Lindb.</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sätern, 425 m V, Vrm</t>
+          <t>Orrbergshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441615.1083664795</v>
+        <v>441373</v>
       </c>
       <c r="R2" t="n">
-        <v>6634045.242033753</v>
+        <v>6634216</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-05-27</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-08-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-05-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-08-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Crister Albinsson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Crister Albinsson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6750082</v>
+        <v>6750091</v>
       </c>
       <c r="B3" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97796</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>2609</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsfliksmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lejeunea cavifolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ehrh.) Lindb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441615.1083664795</v>
+        <v>441615</v>
       </c>
       <c r="R3" t="n">
-        <v>6634045.242033753</v>
+        <v>6634045</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -860,19 +840,9 @@
           <t>2013-05-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2013-05-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,6 +866,685 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>66998875</v>
+      </c>
+      <c r="B4" t="n">
+        <v>96338</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Orrbergshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>441373</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6634216</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Färnebo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2016-08-04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2016-08-04</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>117200372</v>
+      </c>
+      <c r="B5" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Orrbergshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>441623</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6634071</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Färnebo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>117200373</v>
+      </c>
+      <c r="B6" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Orrbergshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>441626</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6634067</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Färnebo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>117200376</v>
+      </c>
+      <c r="B7" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Orrbergshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>441640</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6634065</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Färnebo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6750082</v>
+      </c>
+      <c r="B8" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sätern, 425 m V, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>441615</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6634045</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Färnebo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2013-05-27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2013-05-27</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Crister Albinsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Crister Albinsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>117200371</v>
+      </c>
+      <c r="B9" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Orrbergshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>441623</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6634071</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Färnebo</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>117200374</v>
+      </c>
+      <c r="B10" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Orrbergshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>441640</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6634065</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Färnebo</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45602-2025 artfynd.xlsx
+++ b/artfynd/A 45602-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66998874</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6750091</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66998875</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117200372</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117200373</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117200376</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6750082</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117200371</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,8 +1590,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117200374</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>